--- a/lcr_analyses/clustering/carriers/FLPS/cluster_summaries_pam.xlsx
+++ b/lcr_analyses/clustering/carriers/FLPS/cluster_summaries_pam.xlsx
@@ -12,6 +12,10 @@
     <sheet name="k4" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="k5" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="k6" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="k7" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="k8" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="k9" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="k10" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4524,4 +4528,5856 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>212</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2037799538974757</v>
+      </c>
+      <c r="E2" t="n">
+        <v>24.92857142857143</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1462264150943396</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2216981132075472</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6132075471698113</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.160377358490566</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2122641509433962</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1839622641509434</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1273584905660377</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1650943396226415</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.07075471698113207</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05660377358490566</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.07547169811320754</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.02830188679245283</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.04245283018867924</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1745283018867924</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1037735849056604</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1226415094339623</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.7452830188679245</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.004716981132075472</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.009433962264150943</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.004716981132075472</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.02830188679245283</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1084905660377359</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.406760514424748</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.53610375050958</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.0353461738677772</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.736106346483705</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.08474007724247973</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.04638538616307097</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1531425891181988</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.02561509021323127</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2458344125010792</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>251</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2390438247011952</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2191235059760956</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.749003984063745</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1115537848605578</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8764940239043825</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.09561752988047809</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1235059760956175</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.199203187250996</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.3067729083665339</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.7330677290836654</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8406374501992032</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1474103585657371</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0199203187250996</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2669322709163346</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2828685258964144</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.05179282868525897</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.151394422310757</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.7928286852589641</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.00796812749003984</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0398406374501992</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.01195219123505976</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.06772908366533864</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1752988047808765</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5824561403508772</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.4556962025316456</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1641791044776119</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.04945054945054945</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1849710982658959</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3486842105263158</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.01444043321299639</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1569506726457399</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>62</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>271</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.122568093385214</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2324723247232472</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3357933579335793</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2472324723247233</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.06642066420664207</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2287822878228782</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02214022140221402</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.04059040590405904</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05535055350553506</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.6014760147601476</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6199261992619927</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1180811808118081</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.05535055350553506</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.0959409594095941</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.0996309963099631</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.01845018450184502</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.05904059040590406</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1476014760147601</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.003690036900369004</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.007380073800738007</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.1033210332103321</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.176056338028169</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.7045454545454546</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.3488372093023256</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.07812499999999997</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.4468085106382979</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>58</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>54</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>69</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>270</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1010869293151782</v>
+      </c>
+      <c r="E5" t="n">
+        <v>20.16666666666666</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2185185185185185</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3296296296296296</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.162962962962963</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1481481481481481</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.162962962962963</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.04074074074074074</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.01481481481481482</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1074074074074074</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.09259259259259259</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1037037037037037</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.02962962962962963</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.007407407407407408</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.3111111111111111</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.7185185185185186</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.07777777777777778</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1037037037037037</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1555555555555556</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.01851851851851852</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.003703703703703704</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.003703703703703704</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.05185185185185185</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4716577540106952</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.6324561403508772</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2757936507936508</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.1124604771486059</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.488233665559247</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.06153846153846154</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.1777003484320557</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.02777777777777778</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1132075471698113</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>84</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>76</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>47</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>242</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1321822678843227</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.47413793103448</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2148760330578512</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.256198347107438</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.256198347107438</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.06611570247933884</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3305785123966942</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.03305785123966942</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.08677685950413223</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.07851239669421488</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2355371900826446</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1198347107438017</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9214876033057852</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.09917355371900827</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.01239669421487603</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1322314049586777</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1115702479338843</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.02479338842975207</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.05371900826446281</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1776859504132231</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.02066115702479339</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.004132231404958678</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.02479338842975207</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.115702479338843</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6976911976911977</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4161255411255411</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1568651574803149</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.6698173621250545</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1302173913043478</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3188542227003766</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4807407407407407</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.1772486772486773</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.09706827754378186</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>92</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>272</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2220314014855724</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24.84033613445378</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2352941176470588</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3088235294117647</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7095588235294118</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1654411764705882</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9080882352941176</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.09926470588235294</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.05882352941176471</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2242647058823529</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1176470588235294</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1654411764705882</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2389705882352941</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.06985294117647059</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.01838235294117647</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1948529411764706</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9154411764705882</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.02573529411764706</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.2095588235294118</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.01838235294117647</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.03308823529411765</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1213235294117647</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1911764705882353</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.4929901960784314</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5015174260559094</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1979009207090834</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.08786764705882355</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.6544800814560265</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.07617907148120856</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.06087871982032567</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.1514324254881809</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.008635440388994893</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1810150979762287</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>158</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>179</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2047101449275362</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6312849162011173</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.770949720670391</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6871508379888268</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.664804469273743</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7988826815642458</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1340782122905028</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1284916201117318</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2569832402234637</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7541899441340782</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6312849162011173</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.8212290502793296</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2290502793296089</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.02793296089385475</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2849162011173184</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.776536312849162</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.07262569832402235</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.217877094972067</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7988826815642458</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.02793296089385475</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.0335195530726257</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0111731843575419</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.06145251396648044</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.3240223463687151</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6027397260273972</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4907063197026023</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.178021978021978</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.06024096385542169</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6810730253353204</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1812865497076023</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1616438356164384</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3497536945812808</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.01600000000000001</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1550387596899225</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>47</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>192</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2268788190280395</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.140625</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2395833333333333</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6197916666666666</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1770833333333333</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.203125</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.140625</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1770833333333333</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.078125</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.08333333333333333</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.046875</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1145833333333333</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1145833333333333</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1302083333333333</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.7760416666666666</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.005208333333333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.01041666666666667</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.005208333333333333</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.02604166666666667</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.09895833333333333</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.5165903890160184</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1466871584699453</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.03846153846153846</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.7446343130553656</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.09118625277161863</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.05147302217808672</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1628992628992629</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.03086890243902438</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.2620754716981132</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>105</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>251</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.33333333333333</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2390438247011952</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2191235059760956</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.749003984063745</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1115537848605578</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8764940239043825</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.09561752988047809</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1235059760956175</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.199203187250996</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.3067729083665339</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.7330677290836654</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8406374501992032</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1474103585657371</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.0199203187250996</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2669322709163346</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2828685258964144</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.05179282868525897</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.151394422310757</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.7928286852589641</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.00796812749003984</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.0398406374501992</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.01195219123505976</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.06772908366533864</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1752988047808765</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5824561403508772</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.4556962025316456</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1641791044776119</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.04945054945054945</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1849710982658959</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3486842105263158</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.01444043321299639</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1569506726457399</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>97</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>62</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>269</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1226993865030675</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2304832713754647</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.3345724907063197</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2490706319702602</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.06691449814126393</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.2304832713754647</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.02230483271375465</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.04089219330855019</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05576208178438662</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.5985130111524164</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6245353159851301</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.1189591078066914</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.05576208178438662</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.08921933085501858</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.1003717472118959</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.01858736059479554</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.05947955390334572</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1486988847583643</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.003717472118959108</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.007434944237918215</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.104089219330855</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5740740740740741</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1746031746031746</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.05555555555555555</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.7053571428571429</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.3488372093023256</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.07857142857142857</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.4482758620689655</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>58</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>53</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>220</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1219626211912976</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22.66666666666666</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3545454545454546</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1772727272727273</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1727272727272727</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.1681818181818182</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.01818181818181818</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.06818181818181818</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1318181818181818</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1136363636363636</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1227272727272727</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.03181818181818181</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.00909090909090909</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.1909090909090909</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8590909090909091</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.08636363636363636</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1227272727272727</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1909090909090909</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.02272727272727273</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.004545454545454545</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.004545454545454545</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.06363636363636363</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1727272727272727</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.6051904176904177</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2536262350220727</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.1132075471698113</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5283018867924528</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1015965166908563</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.1880896226415094</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.04173913043478261</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1278964107223989</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>239</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1329588014981273</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19.57142857142857</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2133891213389121</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2552301255230126</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2552301255230126</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.06694560669456066</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.3305439330543933</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.03347280334728033</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.08786610878661087</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.07949790794979079</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2384937238493724</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1213389121338912</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9246861924686193</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.100418410041841</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.01255230125523013</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1255230125523012</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1129707112970711</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.02510460251046025</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.05439330543933055</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1799163179916318</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.02092050209205021</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.004184100418410041</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.02510460251046025</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1087866108786611</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6984126984126984</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.4102564102564102</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.676056338028169</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.1333333333333334</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3207547169811321</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.1759259259259259</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.0995260663507109</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>271</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2224510813594233</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24.85714285714286</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2361623616236162</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3099630996309963</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7084870848708487</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1660516605166052</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9077490774907749</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0996309963099631</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.05904059040590406</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2250922509225092</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1180811808118081</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1660516605166052</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2398523985239852</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.07011070110701106</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.01845018450184502</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1918819188191882</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9188191881918819</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.02583025830258303</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.2103321033210332</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.8265682656826568</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.01845018450184502</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.03321033210332103</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1180811808118081</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1918819188191882</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.4933333333333333</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5009940357852882</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1973684210526316</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.08823529411764706</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.654639175257732</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.07627118644067797</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.06021897810218978</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.1517857142857143</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.009478672985781991</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>157</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>179</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2047101449275362</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23.375</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6312849162011173</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.770949720670391</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6871508379888268</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.664804469273743</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7988826815642458</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1340782122905028</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1284916201117318</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2569832402234637</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7541899441340782</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6312849162011173</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.8212290502793296</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2290502793296089</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.02793296089385475</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.2849162011173184</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.776536312849162</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.07262569832402235</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.217877094972067</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.7988826815642458</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.02793296089385475</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.0335195530726257</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.0111731843575419</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.06145251396648044</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.3240223463687151</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6027397260273972</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4907063197026023</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.178021978021978</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.06024096385542169</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6810730253353204</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1812865497076023</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1616438356164384</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3497536945812808</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.01600000000000001</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1550387596899225</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>47</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03483267521122411</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2763157894736842</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0131578947368421</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.03947368421052631</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0131578947368421</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.8157894736842105</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.06578947368421052</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1184210526315789</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1710526315789474</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.291005291005291</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.5527777777777778</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.03243338008415148</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.2071428571428571</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.07596153846153847</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.02862903225806452</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>224</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.1467700533010693</v>
+      </c>
+      <c r="E2" t="n">
+        <v>21</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1964285714285714</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.2946428571428572</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1964285714285714</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1785714285714286</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.1026785714285714</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.05803571428571429</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1071428571428571</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1919642857142857</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.1473214285714286</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.08035714285714286</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.04910714285714286</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1517857142857143</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1607142857142857</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.02232142857142857</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1696428571428572</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.008928571428571428</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.01339285714285714</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.004464285714285714</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.02678571428571428</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1026785714285714</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4388009049773756</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.538126092574295</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1576510721247563</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.7423963133640553</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.1188235294117647</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.05266805266805267</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1923507141627947</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.05186323472915866</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.1825757575757576</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>91</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>37</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>14</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>213</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.62162162162162</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2253521126760563</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.1830985915492958</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.704225352112676</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1126760563380282</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8215962441314554</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.09389671361502347</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1173708920187793</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2253521126760563</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.2206572769953052</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.7793427230046949</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8356807511737089</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1314553990610329</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.02347417840375587</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2488262910798122</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.3192488262910798</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.06572769953051644</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1830985915492958</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.8685446009389671</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.009389671361502348</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.04694835680751173</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.004694835680751174</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.07981220657276995</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.215962441314554</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5538461538461539</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.4504995458673933</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.0504774897680764</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7018633540372671</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1529271206690561</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1623616236162362</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3209876543209876</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.0218978102189781</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1649484536082474</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>88</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>193</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="E4" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2590673575129533</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6476683937823834</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.2124352331606218</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.04663212435233161</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1398963730569948</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04663212435233161</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.06735751295336788</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05699481865284974</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2797927461139896</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.7046632124352331</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.06217616580310881</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.05181347150259067</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.05181347150259067</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.08808290155440414</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.0310880829015544</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.0310880829015544</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.04663212435233161</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.02072538860103627</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.09326424870466321</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6805555555555556</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.3437500000000001</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.06557377049180328</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.4307692307692308</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.2717391304347826</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>56</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>199</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1134020618556701</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.221105527638191</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3065326633165829</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.2060301507537688</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1457286432160804</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2010050251256282</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.05527638190954774</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.01005025125628141</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.05527638190954774</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.1708542713567839</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1005025125628141</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.1256281407035176</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.03015075376884422</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.01005025125628141</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2060301507537688</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8743718592964824</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.07537688442211055</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.1005025125628141</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1155778894472362</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.01507537688442211</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.005025125628140704</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.005025125628140704</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.06030150753768844</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.1909547738693467</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.5058139534883721</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2682926829268293</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.1228070175438596</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5161290322580645</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.06896551724137931</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.04347826086956521</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1267605633802817</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>54</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>59</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>31</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>191</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1279069767441861</v>
+      </c>
+      <c r="E6" t="n">
+        <v>19</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2041884816753927</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1832460732984293</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2146596858638743</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.07853403141361257</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2460732984293194</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0418848167539267</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.08376963350785341</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.08376963350785341</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.1518324607329843</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.162303664921466</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9476439790575916</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.08900523560209424</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.01570680628272251</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1361256544502618</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.1204188481675393</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.02617801047120419</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.0418848167539267</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1780104712041885</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.02617801047120419</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.005235602094240838</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.01047120418848168</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1204188481675393</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6885245901639344</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.163265306122449</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.03846153846153845</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.676056338028169</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.09523809523809523</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.328042328042328</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4715909090909091</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.2142857142857142</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.1025641025641026</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>75</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>31</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>292</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2291145166058934</v>
+      </c>
+      <c r="E7" t="n">
+        <v>25.47727272727273</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2157534246575342</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.2842465753424658</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7602739726027398</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1678082191780822</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8767123287671232</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1301369863013699</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.0958904109589041</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.113013698630137</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1472602739726027</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.226027397260274</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.07191780821917808</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.02397260273972603</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1849315068493151</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.8767123287671232</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.0136986301369863</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.1952054794520548</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.8116438356164384</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.02054794520547945</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.0273972602739726</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.113013698630137</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1849315068493151</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.4973684210526316</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.4964375</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.1909090909090909</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.0889894419306184</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.6584049833304089</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.07665598290598291</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.06166988473465566</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.1500985637848493</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.01157744827008461</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>179</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>157</v>
+      </c>
+      <c r="C8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2137592137592138</v>
+      </c>
+      <c r="E8" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.6305732484076433</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7898089171974523</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.6687898089171974</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.6942675159235668</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7770700636942676</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1464968152866242</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1210191082802548</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2738853503184713</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.7452229299363057</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.6624203821656051</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.802547770700637</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2165605095541401</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.02547770700636943</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3121019108280255</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.8216560509554141</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.07643312101910828</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2420382165605096</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.8789808917197452</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.02547770700636943</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.03184713375796178</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0.01273885350318471</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.07006369426751592</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.3184713375796178</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.5980066445182725</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4942528735632184</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.178021978021978</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.06358381502890173</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.6835443037974683</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1726121979286536</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.154040404040404</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3390804597701149</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.01550387596899224</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1630434782608696</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>71</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>69</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03470031545741325</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2753623188405797</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2028985507246377</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2608695652173913</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1304347826086956</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01449275362318841</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.04347826086956522</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.01449275362318841</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.8405797101449275</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.07246376811594203</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.01449275362318841</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.02898550724637681</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1594202898550725</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.2962962962962963</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.05263157894736842</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>159</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.148711943793911</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19.69230769230769</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2389937106918239</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2578616352201258</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.119496855345912</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7861635220125787</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.0440251572327044</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.1069182389937107</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.0880503144654088</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9371069182389937</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.270440251572327</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.710691823899371</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1383647798742138</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.006289308176100629</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1572327044025157</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1320754716981132</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.01257861635220126</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.06289308176100629</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1823899371069182</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.01257861635220126</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.006289308176100629</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.01257861635220126</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.01257861635220126</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.09433962264150944</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.7272727272727273</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.1452991452991453</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.04411764705882353</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.7037037037037037</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.2891566265060241</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.2180451127819549</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.5189873417721519</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.07499999999999998</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.09302325581395349</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>42</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AU11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cluster</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>median_n_lcr</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>median_coverage</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>median_mean_lcr_length</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>prop_domain_intrinsic</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>prop_domain_edge</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>prop_domain_adjacent</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>prop_interdomain_linker</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>prop_distal_terminal</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>prop_sig_rg_rgg_repeat_region</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prop_sig_sr_rs_repeat_region</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>prop_sig_gs_rich_neutral_region</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>prop_sig_basic_enriched_region</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>prop_sig_arginine_rich_rna_contact_region</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>prop_sig_acidic_region</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>prop_sig_mixed_charge_polyampholyte</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>prop_sig_polar_linker</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>prop_sig_hydrophobic_region</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_sticker_region</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>prop_sig_aromatic_aggregation_prone_region</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>prop_sig_cation_pi_rich_neighborhood</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>prop_sig_disorder_rich_spacer_region</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>prop_sig_serine_rich_region</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>prop_sig_glutamine_rich_region</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>prop_sig_glycine_rich_region</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>prop_sig_proline_rich_disordered_region</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>prop_sig_unmapped_physicochemical_properties</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>median_frac_polar</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>median_frac_hydrophobic</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>median_frac_strong_hydro</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>median_frac_aromatic</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>median_frac_disorder</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>median_frac_positive</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>median_frac_negative</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>median_fcr</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>median_ncpr</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>median_frac_GS</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>class_mRNA</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>class_unknown</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>class_ribosomal protein</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>class_snRNA</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>class_tRNA</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>class_diverse</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>class_ncRNA</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>class_snoRNA</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>class_pre-rRNA</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>179</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.2156862745098039</v>
+      </c>
+      <c r="E2" t="n">
+        <v>26</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1452513966480447</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.2122905027932961</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.6312849162011173</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.1620111731843575</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.2122905027932961</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2067039106145251</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.1340782122905028</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.1452513966480447</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.0446927374301676</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.05586592178770949</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.0782122905027933</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.02793296089385475</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0446927374301676</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.1173184357541899</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.1005586592178771</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.1173184357541899</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.7877094972067039</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.00558659217877095</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.0111731843575419</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.00558659217877095</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.0223463687150838</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.1005586592178771</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.4230769230769231</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.52046783625731</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.1447368421052632</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.03529411764705882</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.04679376083188908</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.03124999999999999</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>16</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>185</v>
+      </c>
+      <c r="C3" t="n">
+        <v>6</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.1937086092715232</v>
+      </c>
+      <c r="E3" t="n">
+        <v>21.27272727272727</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2648648648648649</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.2108108108108108</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.7783783783783784</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1351351351351351</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9297297297297298</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0918918918918919</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.1027027027027027</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.2054054054054054</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.1837837837837838</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.7783783783783784</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.1243243243243243</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.02702702702702703</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.2540540540540541</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.2486486486486487</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.05405405405405406</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.1675675675675676</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.8540540540540541</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.005405405405405406</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.04324324324324325</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.005405405405405406</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.07027027027027027</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.1837837837837838</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.5491329479768786</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.4504995458673933</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.1682692307692308</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.04901960784313725</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.1596958174904943</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.1590909090909091</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>-0.01612903225806452</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.1612903225806452</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>72</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>51</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>210</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="E4" t="n">
+        <v>23.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6142857142857143</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.1809523809523809</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1523809523809524</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0380952380952381</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.06666666666666667</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.04285714285714286</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.2904761904761905</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.7047619047619048</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.05238095238095238</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.05714285714285714</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.03333333333333333</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.04761904761904762</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.01904761904761905</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0.6390773405698779</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.5669642857142857</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0603030303030303</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.6884181392378114</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.3429276315789473</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.06350806451612903</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.4296703296703297</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.2722332015810277</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.09918032786885247</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>59</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>61</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>197</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1127946127946128</v>
+      </c>
+      <c r="E5" t="n">
+        <v>22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.233502538071066</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.3147208121827411</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1928934010152284</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.1725888324873096</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.2030456852791878</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.04568527918781726</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.005076142131979695</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.07614213197969544</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.116751269035533</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.1065989847715736</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.09137055837563451</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.02538071065989848</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.01015228426395939</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.2131979695431472</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.868020304568528</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.08121827411167512</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.116751269035533</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.1472081218274112</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.01522842639593909</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.005076142131979695</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0.005076142131979695</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0.05583756345177665</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.16751269035533</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0.4935064935064935</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.2676056338028169</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.5172413793103449</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.09999999999999999</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.06451612903225806</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.1206896551724138</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>57</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>57</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>175</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1021505376344086</v>
+      </c>
+      <c r="E6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2171428571428571</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.2228571428571429</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2685714285714286</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.06285714285714286</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.07428571428571429</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.1257142857142857</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.08571428571428572</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.005714285714285714</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.1485714285714286</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.09142857142857143</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.04571428571428571</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.1142857142857143</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0.005714285714285714</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.1085714285714286</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0.6904761904761905</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.391304347826087</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.676056338028169</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.09090909090909088</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>-0.2395209580838323</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.09090909090909088</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>67</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>254</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.2214467314225476</v>
+      </c>
+      <c r="E7" t="n">
+        <v>24.84033613445378</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2401574803149606</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.3031496062992126</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7322834645669292</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.1653543307086614</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9251968503937008</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.1023622047244094</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.05511811023622047</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2204724409448819</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.08661417322834646</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.1692913385826772</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.2165354330708661</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.07480314960629922</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.01574803149606299</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1929133858267716</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9173228346456693</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.01968503937007874</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.2086614173228346</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.8228346456692913</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.01181102362204724</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.03543307086614173</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0.1220472440944882</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.1850393700787402</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0.4866642958748222</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.5063102012270719</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.2025659262501368</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.08925049309664695</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.6544800814560265</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.07307755504436411</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.05832329388420381</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.1470588235294117</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.009961268607773502</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.1781633516716039</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>150</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>58</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>6</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>128</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2094405594405594</v>
+      </c>
+      <c r="E8" t="n">
+        <v>22.07142857142857</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.1484375</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.09375</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.265625</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0703125</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.1171875</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2578125</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.796875</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.390625</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.7421875</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1796875</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.71875</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.0546875</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.2109375</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.890625</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.0390625</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.03125</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0.0859375</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.2734375</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0.6112611859938362</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.4741115196078431</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.1704397163120567</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0.05679723502304147</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.679080459770115</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.1681671004054954</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.1443793911007026</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0.3244495166487648</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0.0223470661672909</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0.1828616352201258</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>49</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>76</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.03483267521122411</v>
+      </c>
+      <c r="E9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2763157894736842</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1842105263157895</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2368421052631579</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0131578947368421</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.03947368421052631</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.0131578947368421</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.8157894736842105</v>
+      </c>
+      <c r="T9" t="n">
+        <v>0.06578947368421052</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.1184210526315789</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0.02631578947368421</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.1710526315789474</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0.291005291005291</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.5527777777777778</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0.03243338008415148</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0.2071428571428571</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0.07596153846153847</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0.02862903225806452</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>22</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>15</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>154</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.1476893052302888</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19.59615384615385</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2467532467532468</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.2467532467532468</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.7792207792207793</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1233766233766234</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7922077922077922</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.1038961038961039</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.08441558441558442</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.9415584415584416</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.7012987012987013</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.006493506493506494</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1558441558441558</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0.1168831168831169</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.06493506493506493</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.006493506493506494</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.01298701298701299</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.09740259740259741</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.7273833222738333</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.04276097074468085</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0.7032669461914745</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.2910136592379583</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.229020979020979</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0.07488317757009344</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>41</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>35</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>139</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2137592137592138</v>
+      </c>
+      <c r="E11" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6546762589928058</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8273381294964028</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.7122302158273381</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.7482014388489209</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7841726618705036</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.1366906474820144</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.1151079136690648</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2805755395683453</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.7050359712230215</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.6906474820143885</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.7841726618705036</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.2302158273381295</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.02877697841726619</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.316546762589928</v>
+      </c>
+      <c r="T11" t="n">
+        <v>0.8057553956834532</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.07913669064748201</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.2302158273381295</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.8633093525179856</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.02877697841726619</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.02158273381294964</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0.01438848920863309</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0.06474820143884892</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.3309352517985611</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.5909909909909909</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.4961089494163424</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0.1786310517529215</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0.05947955390334572</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0.6810730253353204</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.1722054380664653</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.154040404040404</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0.3376623376623377</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0.01123595505617978</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0.1630434782608696</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>61</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>